--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/metrics_default_vs_aae.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8083333333333333</v>
+        <v>0.85</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7535211267605634</v>
+        <v>0.7887323943661971</v>
       </c>
       <c r="D2">
-        <v>0.2651515151515151</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="E2">
         <v>120</v>
